--- a/test/douyin_5.xlsx
+++ b/test/douyin_5.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>抖音直播的时候手机发热严重，烫手</t>
+          <t>抖音客服态度很差，投诉没人理</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>抖音评论的时候网络异常，发出去显示失败</t>
+          <t>抖音买东西货不对板，卖家不退款</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/test/douyin_5.xlsx
+++ b/test/douyin_5.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>抖音刷视频的时候经常卡顿，画面一卡一卡的</t>
+          <t>抖音刷视频的时候经常卡顿，画面一卡一卡的，特别影响观看体验。尤其是在晚上高峰时段，卡顿现象更加严重，有时候视频会暂停好几秒才继续播放，甚至出现画面声音不同步的问题，让人非常烦躁，希望能尽快优化改善。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
